--- a/data/trans_dic/DCD_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/DCD_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,87; 19,57</t>
+          <t>14,01; 19,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,73; 29,69</t>
+          <t>20,93; 29,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,88; 23,91</t>
+          <t>19,43; 24,06</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 14,44</t>
+          <t>4,92; 14,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,25; 29,92</t>
+          <t>25,18; 29,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,17; 21,02</t>
+          <t>11,74; 21,03</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,09; 14,99</t>
+          <t>10,08; 15,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,37; 29,03</t>
+          <t>10,39; 29,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,12; 20,67</t>
+          <t>11,86; 20,88</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,0; 17,82</t>
+          <t>13,13; 17,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,33; 29,73</t>
+          <t>21,6; 29,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,11; 23,39</t>
+          <t>18,95; 23,29</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,42; 14,94</t>
+          <t>10,55; 15,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,8; 27,7</t>
+          <t>20,58; 27,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,11; 21,21</t>
+          <t>16,92; 21,14</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>88140; 124384</t>
+          <t>89048; 125049</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>150369; 215322</t>
+          <t>151807; 216623</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>256930; 325318</t>
+          <t>264463; 327383</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71834; 172201</t>
+          <t>58654; 170250</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>242014; 286790</t>
+          <t>241388; 286640</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>261774; 452219</t>
+          <t>252678; 452472</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>71070; 105612</t>
+          <t>71018; 105759</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>115456; 270997</t>
+          <t>97017; 270890</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>198577; 338607</t>
+          <t>194291; 342019</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>120470; 165177</t>
+          <t>121691; 162271</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>233515; 325511</t>
+          <t>236454; 326154</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>386375; 472920</t>
+          <t>383096; 470906</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>360611; 516813</t>
+          <t>364903; 519297</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>772295; 1028292</t>
+          <t>764091; 1028185</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1227473; 1521176</t>
+          <t>1213709; 1516243</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DCD_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/DCD_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,01; 19,68</t>
+          <t>13,88; 19,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,93; 29,87</t>
+          <t>25,77; 31,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,43; 24,06</t>
+          <t>20,58; 24,32</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 14,27</t>
+          <t>11,1; 15,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,18; 29,9</t>
+          <t>24,94; 29,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,74; 21,03</t>
+          <t>18,69; 21,96</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,08; 15,01</t>
+          <t>10,1; 14,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 29,02</t>
+          <t>25,94; 31,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,86; 20,88</t>
+          <t>18,71; 22,5</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,13; 17,51</t>
+          <t>12,88; 17,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,6; 29,79</t>
+          <t>26,1; 30,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,95; 23,29</t>
+          <t>20,51; 23,86</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,55; 15,01</t>
+          <t>12,96; 15,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,58; 27,7</t>
+          <t>26,92; 29,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,92; 21,14</t>
+          <t>20,32; 22,12</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>105998</t>
+          <t>113168</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>192653</t>
+          <t>206837</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>298651</t>
+          <t>320005</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89048; 125049</t>
+          <t>95867; 132690</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>151807; 216623</t>
+          <t>189221; 228119</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>264463; 327383</t>
+          <t>293248; 346523</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>127906</t>
+          <t>136471</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>263884</t>
+          <t>292452</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>391791</t>
+          <t>428923</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58654; 170250</t>
+          <t>116452; 160202</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>241388; 286640</t>
+          <t>267172; 318014</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>252678; 452472</t>
+          <t>396224; 465726</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86912</t>
+          <t>98977</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>201374</t>
+          <t>233528</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288287</t>
+          <t>332505</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>71018; 105759</t>
+          <t>81110; 119287</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>97017; 270890</t>
+          <t>210673; 258372</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>194291; 342019</t>
+          <t>302184; 363523</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>141763</t>
+          <t>147722</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>291634</t>
+          <t>317420</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>433397</t>
+          <t>465142</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>121691; 162271</t>
+          <t>127568; 170685</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>236454; 326154</t>
+          <t>292060; 345331</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>383096; 470906</t>
+          <t>432584; 503198</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>462580</t>
+          <t>496338</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>949546</t>
+          <t>1050237</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1412125</t>
+          <t>1546575</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>364903; 519297</t>
+          <t>457883; 543216</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>764091; 1028185</t>
+          <t>1006147; 1101531</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1213709; 1516243</t>
+          <t>1477371; 1607726</t>
         </is>
       </c>
     </row>
